--- a/outputs/debug/judgements/excel_overviews/overview_simple.xlsx
+++ b/outputs/debug/judgements/excel_overviews/overview_simple.xlsx
@@ -8,16 +8,18 @@
   </bookViews>
   <sheets>
     <sheet name="ASR-Overview" sheetId="1" r:id="rId1"/>
-    <sheet name="AASR-Overview" sheetId="2" r:id="rId2"/>
-    <sheet name="FR-Overview" sheetId="3" r:id="rId3"/>
-    <sheet name="CR-Overview" sheetId="4" r:id="rId4"/>
+    <sheet name="ASR_WITH_TIES-Overview" sheetId="2" r:id="rId2"/>
+    <sheet name="AASR-Overview" sheetId="3" r:id="rId3"/>
+    <sheet name="AASR_WITH_TIES-Overview" sheetId="4" r:id="rId4"/>
+    <sheet name="FR-Overview" sheetId="5" r:id="rId5"/>
+    <sheet name="CR-Overview" sheetId="6" r:id="rId6"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="367">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="648" uniqueCount="540">
   <si>
     <t>vs_Llama-2-7b-chat-hf</t>
   </si>
@@ -46,385 +48,753 @@
     <t>Judge Model</t>
   </si>
   <si>
+    <t>Mistral-Small-3.2-24B-Instruct-2506</t>
+  </si>
+  <si>
+    <t>Qwen3-4B-Instruct-2507</t>
+  </si>
+  <si>
+    <t>Llama-3.3-70B-Instruct</t>
+  </si>
+  <si>
+    <t>gemini-2.5-flash</t>
+  </si>
+  <si>
+    <t>phi-4</t>
+  </si>
+  <si>
     <t>Llama-3.1-8B-Instruct</t>
   </si>
   <si>
-    <t>Llama-3.3-70B-Instruct</t>
-  </si>
-  <si>
-    <t>Qwen3-4B-Instruct-2507</t>
+    <t>claude-opus-4-5-20251101</t>
+  </si>
+  <si>
+    <t>Mistral-7B-Instruct-v0.3</t>
   </si>
   <si>
     <t>Qwen3-Next-80B-A3B-Instruct</t>
   </si>
   <si>
-    <t>Mistral-7B-Instruct-v0.3</t>
-  </si>
-  <si>
-    <t>Mistral-Small-3.2-24B-Instruct-2506</t>
-  </si>
-  <si>
-    <t>phi-4</t>
-  </si>
-  <si>
-    <t>gemini-2.5-flash</t>
+    <t>gemini-2.5-pro</t>
   </si>
   <si>
     <t>claude-haiku-4-5-20251001</t>
   </si>
   <si>
-    <t>claude-opus-4-5-20251101</t>
-  </si>
-  <si>
-    <t>gemini-2.5-pro</t>
+    <t>ASR: 0.07
+V1: 135 V2: 5 Vties: 2</t>
+  </si>
+  <si>
+    <t>ASR: 0.24
+V1: 129 V2: 6 Vties: 7</t>
+  </si>
+  <si>
+    <t>ASR: 0.10
+V1: 123 V2: 7 Vties: 12</t>
+  </si>
+  <si>
+    <t>ASR: 0.08
+V1: 133 V2: 6 Vties: 3</t>
+  </si>
+  <si>
+    <t>ASR: 0.25
+V1: 134 V2: 5 Vties: 3</t>
   </si>
   <si>
     <t>ASR: 0.30
 V1: 107 V2: 13 Vties: 13</t>
   </si>
   <si>
-    <t>ASR: 0.10
-V1: 123 V2: 7 Vties: 12</t>
-  </si>
-  <si>
-    <t>ASR: 0.24
-V1: 129 V2: 6 Vties: 7</t>
+    <t>ASR: 0.04
+V1: 127 V2: 2 Vties: 12</t>
+  </si>
+  <si>
+    <t>ASR: 0.36
+V1: 107 V2: 11 Vties: 24</t>
   </si>
   <si>
     <t>ASR: 0.09
 V1: 133 V2: 3 Vties: 6</t>
   </si>
   <si>
-    <t>ASR: 0.36
-V1: 107 V2: 11 Vties: 24</t>
-  </si>
-  <si>
-    <t>ASR: 0.07
-V1: 135 V2: 5 Vties: 2</t>
-  </si>
-  <si>
-    <t>ASR: 0.25
-V1: 134 V2: 5 Vties: 3</t>
-  </si>
-  <si>
-    <t>ASR: 0.08
-V1: 133 V2: 6 Vties: 3</t>
+    <t>ASR: 0.05
+V1: 133 V2: 4 Vties: 5</t>
   </si>
   <si>
     <t>ASR: 0.12
 V1: 133 V2: 5 Vties: 3</t>
   </si>
   <si>
-    <t>ASR: 0.04
-V1: 127 V2: 2 Vties: 12</t>
-  </si>
-  <si>
-    <t>ASR: 0.05
-V1: 133 V2: 4 Vties: 5</t>
+    <t>ASR: 0.30
+V1: 88 V2: 31 Vties: 23</t>
+  </si>
+  <si>
+    <t>ASR: 0.51
+V1: 85 V2: 33 Vties: 24</t>
+  </si>
+  <si>
+    <t>ASR: 0.37
+V1: 41 V2: 57 Vties: 44</t>
+  </si>
+  <si>
+    <t>ASR: 0.22
+V1: 94 V2: 36 Vties: 12</t>
+  </si>
+  <si>
+    <t>ASR: 0.49
+V1: 98 V2: 36 Vties: 8</t>
   </si>
   <si>
     <t>ASR: 0.49
 V1: 79 V2: 39 Vties: 22</t>
   </si>
   <si>
-    <t>ASR: 0.37
-V1: 41 V2: 57 Vties: 44</t>
-  </si>
-  <si>
-    <t>ASR: 0.51
-V1: 85 V2: 33 Vties: 24</t>
+    <t>ASR: 0.11
+V1: 76 V2: 22 Vties: 41</t>
+  </si>
+  <si>
+    <t>ASR: 0.41
+V1: 71 V2: 21 Vties: 50</t>
   </si>
   <si>
     <t>ASR: 0.13
 V1: 82 V2: 30 Vties: 26</t>
   </si>
   <si>
-    <t>ASR: 0.41
-V1: 71 V2: 21 Vties: 50</t>
-  </si>
-  <si>
-    <t>ASR: 0.30
-V1: 88 V2: 31 Vties: 23</t>
-  </si>
-  <si>
-    <t>ASR: 0.49
-V1: 98 V2: 36 Vties: 8</t>
-  </si>
-  <si>
-    <t>ASR: 0.22
-V1: 94 V2: 36 Vties: 12</t>
+    <t>ASR: 0.10
+V1: 90 V2: 26 Vties: 26</t>
   </si>
   <si>
     <t>ASR: 0.24
 V1: 96 V2: 37 Vties: 9</t>
   </si>
   <si>
-    <t>ASR: 0.11
-V1: 76 V2: 22 Vties: 41</t>
-  </si>
-  <si>
-    <t>ASR: 0.10
-V1: 90 V2: 26 Vties: 26</t>
+    <t>ASR: 0.28
+V1: 90 V2: 36 Vties: 16</t>
+  </si>
+  <si>
+    <t>ASR: 0.46
+V1: 96 V2: 30 Vties: 16</t>
+  </si>
+  <si>
+    <t>ASR: 0.27
+V1: 73 V2: 35 Vties: 34</t>
+  </si>
+  <si>
+    <t>ASR: 0.24
+V1: 112 V2: 23 Vties: 7</t>
+  </si>
+  <si>
+    <t>ASR: 0.55
+V1: 107 V2: 24 Vties: 11</t>
   </si>
   <si>
     <t>ASR: 0.50
 V1: 74 V2: 25 Vties: 34</t>
   </si>
   <si>
-    <t>ASR: 0.27
-V1: 73 V2: 35 Vties: 34</t>
-  </si>
-  <si>
-    <t>ASR: 0.46
-V1: 96 V2: 30 Vties: 16</t>
+    <t>ASR: 0.13
+V1: 85 V2: 13 Vties: 42</t>
+  </si>
+  <si>
+    <t>ASR: 0.63
+V1: 65 V2: 34 Vties: 43</t>
   </si>
   <si>
     <t>ASR: 0.22
 V1: 96 V2: 23 Vties: 23</t>
   </si>
   <si>
-    <t>ASR: 0.63
-V1: 65 V2: 34 Vties: 43</t>
-  </si>
-  <si>
-    <t>ASR: 0.28
-V1: 90 V2: 36 Vties: 16</t>
-  </si>
-  <si>
-    <t>ASR: 0.55
-V1: 107 V2: 24 Vties: 11</t>
-  </si>
-  <si>
-    <t>ASR: 0.24
-V1: 112 V2: 23 Vties: 7</t>
+    <t>ASR: 0.18
+V1: 102 V2: 14 Vties: 26</t>
   </si>
   <si>
     <t>ASR: 0.23
 V1: 103 V2: 23 Vties: 15</t>
   </si>
   <si>
-    <t>ASR: 0.13
-V1: 85 V2: 13 Vties: 42</t>
-  </si>
-  <si>
-    <t>ASR: 0.18
-V1: 102 V2: 14 Vties: 26</t>
+    <t>ASR: 0.02
+V1: 140 V2: 1 Vties: 1</t>
+  </si>
+  <si>
+    <t>ASR: 0.06
+V1: 136 V2: 3 Vties: 3</t>
+  </si>
+  <si>
+    <t>ASR: 0.05
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
+    <t>ASR: 0.01
+V1: 141 V2: 0 Vties: 1</t>
+  </si>
+  <si>
+    <t>ASR: 0.07
+V1: 138 V2: 1 Vties: 3</t>
   </si>
   <si>
     <t>ASR: 0.17
 V1: 126 V2: 7 Vties: 7</t>
   </si>
   <si>
-    <t>ASR: 0.05
-V1: 133 V2: 3 Vties: 6</t>
-  </si>
-  <si>
-    <t>ASR: 0.06
-V1: 136 V2: 3 Vties: 3</t>
+    <t>ASR: 0.00
+V1: 141 V2: 0 Vties: 1</t>
+  </si>
+  <si>
+    <t>ASR: 0.21
+V1: 111 V2: 14 Vties: 17</t>
   </si>
   <si>
     <t>ASR: 0.01
 V1: 140 V2: 0 Vties: 2</t>
   </si>
   <si>
-    <t>ASR: 0.21
-V1: 111 V2: 14 Vties: 17</t>
-  </si>
-  <si>
-    <t>ASR: 0.02
-V1: 140 V2: 1 Vties: 1</t>
-  </si>
-  <si>
-    <t>ASR: 0.07
-V1: 138 V2: 1 Vties: 3</t>
-  </si>
-  <si>
-    <t>ASR: 0.01
-V1: 141 V2: 0 Vties: 1</t>
-  </si>
-  <si>
-    <t>ASR: 0.00
-V1: 141 V2: 0 Vties: 1</t>
-  </si>
-  <si>
     <t>ASR: 0.01
 V1: 142 V2: 0 Vties: 0</t>
   </si>
   <si>
+    <t>ASR: 0.33
+V1: 60 V2: 68 Vties: 14</t>
+  </si>
+  <si>
+    <t>ASR: 0.39
+V1: 61 V2: 65 Vties: 16</t>
+  </si>
+  <si>
+    <t>ASR: 0.14
+V1: 28 V2: 83 Vties: 31</t>
+  </si>
+  <si>
+    <t>ASR: 0.18
+V1: 78 V2: 58 Vties: 6</t>
+  </si>
+  <si>
+    <t>ASR: 0.59
+V1: 51 V2: 70 Vties: 21</t>
+  </si>
+  <si>
     <t>ASR: 0.61
 V1: 49 V2: 69 Vties: 17</t>
   </si>
   <si>
-    <t>ASR: 0.14
-V1: 28 V2: 83 Vties: 31</t>
-  </si>
-  <si>
-    <t>ASR: 0.39
-V1: 61 V2: 65 Vties: 16</t>
+    <t>ASR: 0.13
+V1: 67 V2: 40 Vties: 32</t>
+  </si>
+  <si>
+    <t>ASR: 0.57
+V1: 47 V2: 50 Vties: 45</t>
   </si>
   <si>
     <t>ASR: 0.20
 V1: 59 V2: 64 Vties: 17</t>
   </si>
   <si>
-    <t>ASR: 0.57
-V1: 47 V2: 50 Vties: 45</t>
-  </si>
-  <si>
-    <t>ASR: 0.33
-V1: 60 V2: 68 Vties: 14</t>
-  </si>
-  <si>
-    <t>ASR: 0.59
-V1: 51 V2: 70 Vties: 21</t>
-  </si>
-  <si>
-    <t>ASR: 0.18
-V1: 78 V2: 58 Vties: 6</t>
+    <t>ASR: 0.20
+V1: 66 V2: 47 Vties: 29</t>
   </si>
   <si>
     <t>ASR: 0.31
 V1: 75 V2: 57 Vties: 10</t>
   </si>
   <si>
-    <t>ASR: 0.13
-V1: 67 V2: 40 Vties: 32</t>
-  </si>
-  <si>
-    <t>ASR: 0.20
-V1: 66 V2: 47 Vties: 29</t>
+    <t>ASR: 0.18
+V1: 123 V2: 15 Vties: 4</t>
+  </si>
+  <si>
+    <t>ASR: 0.28
+V1: 117 V2: 13 Vties: 12</t>
+  </si>
+  <si>
+    <t>ASR: 0.11
+V1: 115 V2: 12 Vties: 15</t>
+  </si>
+  <si>
+    <t>ASR: 0.27
+V1: 41 V2: 43 Vties: 58</t>
+  </si>
+  <si>
+    <t>ASR: 0.44
+V1: 124 V2: 12 Vties: 6</t>
   </si>
   <si>
     <t>ASR: 0.40
 V1: 99 V2: 21 Vties: 17</t>
   </si>
   <si>
-    <t>ASR: 0.11
-V1: 115 V2: 12 Vties: 15</t>
-  </si>
-  <si>
-    <t>ASR: 0.28
-V1: 117 V2: 13 Vties: 12</t>
+    <t>ASR: 0.04
+V1: 121 V2: 3 Vties: 15</t>
+  </si>
+  <si>
+    <t>ASR: 0.38
+V1: 88 V2: 21 Vties: 33</t>
   </si>
   <si>
     <t>ASR: 0.12
 V1: 128 V2: 7 Vties: 7</t>
   </si>
   <si>
-    <t>ASR: 0.38
-V1: 88 V2: 21 Vties: 33</t>
-  </si>
-  <si>
-    <t>ASR: 0.18
-V1: 123 V2: 15 Vties: 4</t>
-  </si>
-  <si>
-    <t>ASR: 0.44
-V1: 124 V2: 12 Vties: 6</t>
-  </si>
-  <si>
-    <t>ASR: 0.27
-V1: 41 V2: 43 Vties: 58</t>
+    <t>ASR: 0.05
+V1: 125 V2: 6 Vties: 11</t>
   </si>
   <si>
     <t>ASR: 0.12
 V1: 128 V2: 12 Vties: 2</t>
   </si>
   <si>
-    <t>ASR: 0.04
-V1: 121 V2: 3 Vties: 15</t>
-  </si>
-  <si>
-    <t>ASR: 0.05
-V1: 125 V2: 6 Vties: 11</t>
+    <t>ASR: 0.30
+V1: 89 V2: 32 Vties: 21</t>
+  </si>
+  <si>
+    <t>ASR: 0.67
+V1: 87 V2: 35 Vties: 20</t>
+  </si>
+  <si>
+    <t>ASR: 0.26
+V1: 77 V2: 34 Vties: 31</t>
+  </si>
+  <si>
+    <t>ASR: 0.29
+V1: 92 V2: 43 Vties: 7</t>
+  </si>
+  <si>
+    <t>ASR: 0.79
+V1: 95 V2: 33 Vties: 14</t>
   </si>
   <si>
     <t>ASR: 0.65
 V1: 62 V2: 46 Vties: 21</t>
   </si>
   <si>
-    <t>ASR: 0.26
-V1: 77 V2: 34 Vties: 31</t>
-  </si>
-  <si>
-    <t>ASR: 0.67
-V1: 87 V2: 35 Vties: 20</t>
+    <t>ASR: 0.17
+V1: 70 V2: 19 Vties: 52</t>
+  </si>
+  <si>
+    <t>ASR: 0.41
+V1: 39 V2: 26 Vties: 77</t>
   </si>
   <si>
     <t>ASR: 0.32
 V1: 94 V2: 24 Vties: 20</t>
   </si>
   <si>
-    <t>ASR: 0.41
-V1: 39 V2: 26 Vties: 77</t>
-  </si>
-  <si>
-    <t>ASR: 0.30
-V1: 89 V2: 32 Vties: 21</t>
-  </si>
-  <si>
-    <t>ASR: 0.79
-V1: 95 V2: 33 Vties: 14</t>
-  </si>
-  <si>
-    <t>ASR: 0.29
-V1: 92 V2: 43 Vties: 7</t>
+    <t>ASR: 0.24
+V1: 79 V2: 28 Vties: 35</t>
   </si>
   <si>
     <t>ASR: 0.32
 V1: 84 V2: 43 Vties: 15</t>
   </si>
   <si>
-    <t>ASR: 0.17
-V1: 70 V2: 19 Vties: 52</t>
-  </si>
-  <si>
-    <t>ASR: 0.24
-V1: 79 V2: 28 Vties: 35</t>
+    <t>ASR: 0.33
+V1: 125 V2: 8 Vties: 9</t>
+  </si>
+  <si>
+    <t>ASR: 0.41
+V1: 101 V2: 1 Vties: 40</t>
+  </si>
+  <si>
+    <t>ASR: 0.27
+V1: 107 V2: 2 Vties: 33</t>
+  </si>
+  <si>
+    <t>ASR: 0.09
+V1: 140 V2: 1 Vties: 1</t>
+  </si>
+  <si>
+    <t>ASR: 0.55
+V1: 130 V2: 2 Vties: 10</t>
   </si>
   <si>
     <t>ASR: 0.56
 V1: 101 V2: 11 Vties: 24</t>
   </si>
   <si>
-    <t>ASR: 0.27
-V1: 107 V2: 2 Vties: 33</t>
-  </si>
-  <si>
-    <t>ASR: 0.41
-V1: 101 V2: 1 Vties: 40</t>
+    <t>ASR: 0.04
+V1: 141 V2: 1 Vties: 0</t>
+  </si>
+  <si>
+    <t>ASR: 0.54
+V1: 61 V2: 26 Vties: 54</t>
   </si>
   <si>
     <t>ASR: 0.28
 V1: 136 V2: 1 Vties: 5</t>
   </si>
   <si>
-    <t>ASR: 0.54
-V1: 61 V2: 26 Vties: 54</t>
-  </si>
-  <si>
-    <t>ASR: 0.33
-V1: 125 V2: 8 Vties: 9</t>
-  </si>
-  <si>
-    <t>ASR: 0.55
-V1: 130 V2: 2 Vties: 10</t>
-  </si>
-  <si>
-    <t>ASR: 0.09
-V1: 140 V2: 1 Vties: 1</t>
+    <t>ASR: 0.06
+V1: 139 V2: 0 Vties: 3</t>
   </si>
   <si>
     <t>ASR: 0.16
 V1: 139 V2: 2 Vties: 0</t>
   </si>
   <si>
-    <t>ASR: 0.04
+    <t>ASR_WITH_TIES: 0.09
+V1: 135 V2: 5 Vties: 2</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.25
+V1: 129 V2: 6 Vties: 7</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.15
+V1: 123 V2: 7 Vties: 12</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.09
+V1: 133 V2: 6 Vties: 3</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.27
+V1: 134 V2: 5 Vties: 3</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.34
+V1: 107 V2: 13 Vties: 13</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.06
+V1: 127 V2: 2 Vties: 12</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.40
+V1: 107 V2: 11 Vties: 24</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.12
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.06
+V1: 133 V2: 4 Vties: 5</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.12
+V1: 133 V2: 5 Vties: 3</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.36
+V1: 88 V2: 31 Vties: 23</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.59
+V1: 85 V2: 33 Vties: 24</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.47
+V1: 41 V2: 57 Vties: 44</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.29
+V1: 94 V2: 36 Vties: 12</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.52
+V1: 98 V2: 36 Vties: 8</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.57
+V1: 79 V2: 39 Vties: 22</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.24
+V1: 76 V2: 22 Vties: 41</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.51
+V1: 71 V2: 21 Vties: 50</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.24
+V1: 82 V2: 30 Vties: 26</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.21
+V1: 90 V2: 26 Vties: 26</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.28
+V1: 96 V2: 37 Vties: 9</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.29
+V1: 90 V2: 36 Vties: 16</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.52
+V1: 96 V2: 30 Vties: 16</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.42
+V1: 73 V2: 35 Vties: 34</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.28
+V1: 112 V2: 23 Vties: 7</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.58
+V1: 107 V2: 24 Vties: 11</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.54
+V1: 74 V2: 25 Vties: 34</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.27
+V1: 85 V2: 13 Vties: 42</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.61
+V1: 65 V2: 34 Vties: 43</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.27
+V1: 96 V2: 23 Vties: 23</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.27
+V1: 102 V2: 14 Vties: 26</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.29
+V1: 103 V2: 23 Vties: 15</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.03
+V1: 140 V2: 1 Vties: 1</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.07
+V1: 136 V2: 3 Vties: 3</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.09
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.01
+V1: 141 V2: 0 Vties: 1</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.07
+V1: 138 V2: 1 Vties: 3</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.17
+V1: 126 V2: 7 Vties: 7</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.00
+V1: 141 V2: 0 Vties: 1</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.24
+V1: 111 V2: 14 Vties: 17</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.02
+V1: 140 V2: 0 Vties: 2</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.01
+V1: 142 V2: 0 Vties: 0</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.41
+V1: 60 V2: 68 Vties: 14</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.51
+V1: 61 V2: 65 Vties: 16</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.37
+V1: 28 V2: 83 Vties: 31</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.21
+V1: 78 V2: 58 Vties: 6</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.65
+V1: 51 V2: 70 Vties: 21</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.68
+V1: 49 V2: 69 Vties: 17</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.26
+V1: 67 V2: 40 Vties: 32</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.62
+V1: 47 V2: 50 Vties: 45</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.26
+V1: 59 V2: 64 Vties: 17</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.33
+V1: 66 V2: 47 Vties: 29</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.36
+V1: 75 V2: 57 Vties: 10</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.20
+V1: 123 V2: 15 Vties: 4</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.33
+V1: 117 V2: 13 Vties: 12</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.19
+V1: 115 V2: 12 Vties: 15</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.32
+V1: 41 V2: 43 Vties: 58</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.47
+V1: 124 V2: 12 Vties: 6</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.43
+V1: 99 V2: 21 Vties: 17</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.08
+V1: 121 V2: 3 Vties: 15</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.46
+V1: 88 V2: 21 Vties: 33</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.15
+V1: 128 V2: 7 Vties: 7</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.07
+V1: 125 V2: 6 Vties: 11</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.13
+V1: 128 V2: 12 Vties: 2</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.34
+V1: 89 V2: 32 Vties: 21</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.68
+V1: 87 V2: 35 Vties: 20</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.35
+V1: 77 V2: 34 Vties: 31</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.31
+V1: 92 V2: 43 Vties: 7</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.80
+V1: 95 V2: 33 Vties: 14</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.69
+V1: 62 V2: 46 Vties: 21</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.30
+V1: 70 V2: 19 Vties: 52</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.50
+V1: 39 V2: 26 Vties: 77</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.37
+V1: 94 V2: 24 Vties: 20</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.33
+V1: 79 V2: 28 Vties: 35</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.38
+V1: 84 V2: 43 Vties: 15</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.35
+V1: 125 V2: 8 Vties: 9</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.52
+V1: 101 V2: 1 Vties: 40</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.31
+V1: 107 V2: 2 Vties: 33</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.09
+V1: 140 V2: 1 Vties: 1</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.56
+V1: 130 V2: 2 Vties: 10</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.58
+V1: 101 V2: 11 Vties: 24</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.04
 V1: 141 V2: 1 Vties: 0</t>
   </si>
   <si>
-    <t>ASR: 0.06
+    <t>ASR_WITH_TIES: 0.63
+V1: 61 V2: 26 Vties: 54</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.29
+V1: 136 V2: 1 Vties: 5</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.06
 V1: 139 V2: 0 Vties: 3</t>
+  </si>
+  <si>
+    <t>ASR_WITH_TIES: 0.16
+V1: 139 V2: 2 Vties: 0</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 135 V2: 5 Vties: 2</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 129 V2: 6 Vties: 7</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 123 V2: 7 Vties: 12</t>
+  </si>
+  <si>
+    <t>AASR: 0.17
+V1: 133 V2: 6 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 134 V2: 5 Vties: 3</t>
   </si>
   <si>
     <t>AASR: 0.31
@@ -432,15 +802,7 @@
   </si>
   <si>
     <t>AASR: 0.00
-V1: 123 V2: 7 Vties: 12</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 129 V2: 6 Vties: 7</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 133 V2: 3 Vties: 6</t>
+V1: 127 V2: 2 Vties: 12</t>
   </si>
   <si>
     <t>AASR: 0.27
@@ -448,71 +810,79 @@
   </si>
   <si>
     <t>AASR: 0.00
-V1: 135 V2: 5 Vties: 2</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 134 V2: 5 Vties: 3</t>
-  </si>
-  <si>
-    <t>AASR: 0.17
-V1: 133 V2: 6 Vties: 3</t>
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 133 V2: 4 Vties: 5</t>
   </si>
   <si>
     <t>AASR: 0.00
 V1: 133 V2: 5 Vties: 3</t>
   </si>
   <si>
-    <t>AASR: 0.00
-V1: 127 V2: 2 Vties: 12</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 133 V2: 4 Vties: 5</t>
+    <t>AASR: 0.03
+V1: 88 V2: 31 Vties: 23</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 85 V2: 33 Vties: 24</t>
+  </si>
+  <si>
+    <t>AASR: 0.02
+V1: 41 V2: 57 Vties: 44</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 94 V2: 36 Vties: 12</t>
+  </si>
+  <si>
+    <t>AASR: 0.03
+V1: 98 V2: 36 Vties: 8</t>
   </si>
   <si>
     <t>AASR: 0.05
 V1: 79 V2: 39 Vties: 22</t>
   </si>
   <si>
-    <t>AASR: 0.02
-V1: 41 V2: 57 Vties: 44</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 85 V2: 33 Vties: 24</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 82 V2: 30 Vties: 26</t>
+    <t>AASR: 0.05
+V1: 76 V2: 22 Vties: 41</t>
   </si>
   <si>
     <t>AASR: 0.19
 V1: 71 V2: 21 Vties: 50</t>
   </si>
   <si>
-    <t>AASR: 0.03
-V1: 88 V2: 31 Vties: 23</t>
-  </si>
-  <si>
-    <t>AASR: 0.03
-V1: 98 V2: 36 Vties: 8</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 94 V2: 36 Vties: 12</t>
+    <t>AASR: 0.00
+V1: 82 V2: 30 Vties: 26</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 90 V2: 26 Vties: 26</t>
   </si>
   <si>
     <t>AASR: 0.03
 V1: 96 V2: 37 Vties: 9</t>
   </si>
   <si>
-    <t>AASR: 0.05
-V1: 76 V2: 22 Vties: 41</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 90 V2: 26 Vties: 26</t>
+    <t>AASR: 0.14
+V1: 90 V2: 36 Vties: 16</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 96 V2: 30 Vties: 16</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 73 V2: 35 Vties: 34</t>
+  </si>
+  <si>
+    <t>AASR: 0.04
+V1: 112 V2: 23 Vties: 7</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 107 V2: 24 Vties: 11</t>
   </si>
   <si>
     <t>AASR: 0.20
@@ -520,119 +890,119 @@
   </si>
   <si>
     <t>AASR: 0.00
-V1: 73 V2: 35 Vties: 34</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 96 V2: 30 Vties: 16</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 96 V2: 23 Vties: 23</t>
+V1: 85 V2: 13 Vties: 42</t>
   </si>
   <si>
     <t>AASR: 0.12
 V1: 65 V2: 34 Vties: 43</t>
   </si>
   <si>
-    <t>AASR: 0.14
-V1: 90 V2: 36 Vties: 16</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 107 V2: 24 Vties: 11</t>
-  </si>
-  <si>
-    <t>AASR: 0.04
-V1: 112 V2: 23 Vties: 7</t>
+    <t>AASR: 0.00
+V1: 96 V2: 23 Vties: 23</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 102 V2: 14 Vties: 26</t>
   </si>
   <si>
     <t>AASR: 0.00
 V1: 103 V2: 23 Vties: 15</t>
   </si>
   <si>
-    <t>AASR: 0.00
-V1: 85 V2: 13 Vties: 42</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 102 V2: 14 Vties: 26</t>
+    <t>AASR: 1.00
+V1: 140 V2: 1 Vties: 1</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 136 V2: 3 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 141 V2: 0 Vties: 1</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 138 V2: 1 Vties: 3</t>
   </si>
   <si>
     <t>AASR: 0.43
 V1: 126 V2: 7 Vties: 7</t>
   </si>
   <si>
-    <t>AASR: 0.00
-V1: 136 V2: 3 Vties: 3</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 140 V2: 0 Vties: 2</t>
-  </si>
-  <si>
     <t>AASR: 0.07
 V1: 111 V2: 14 Vties: 17</t>
   </si>
   <si>
-    <t>AASR: 1.00
-V1: 140 V2: 1 Vties: 1</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 138 V2: 1 Vties: 3</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 141 V2: 0 Vties: 1</t>
+    <t>AASR: 0.00
+V1: 140 V2: 0 Vties: 2</t>
   </si>
   <si>
     <t>AASR: 0.00
 V1: 142 V2: 0 Vties: 0</t>
+  </si>
+  <si>
+    <t>AASR: 0.07
+V1: 60 V2: 68 Vties: 14</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 61 V2: 65 Vties: 16</t>
+  </si>
+  <si>
+    <t>AASR: 0.01
+V1: 28 V2: 83 Vties: 31</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 78 V2: 58 Vties: 6</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 51 V2: 70 Vties: 21</t>
   </si>
   <si>
     <t>AASR: 0.06
 V1: 49 V2: 69 Vties: 17</t>
   </si>
   <si>
-    <t>AASR: 0.01
-V1: 28 V2: 83 Vties: 31</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 61 V2: 65 Vties: 16</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 59 V2: 64 Vties: 17</t>
+    <t>AASR: 0.00
+V1: 67 V2: 40 Vties: 32</t>
   </si>
   <si>
     <t>AASR: 0.06
 V1: 47 V2: 50 Vties: 45</t>
   </si>
   <si>
-    <t>AASR: 0.07
-V1: 60 V2: 68 Vties: 14</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 51 V2: 70 Vties: 21</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 78 V2: 58 Vties: 6</t>
+    <t>AASR: 0.00
+V1: 59 V2: 64 Vties: 17</t>
+  </si>
+  <si>
+    <t>AASR: 0.02
+V1: 66 V2: 47 Vties: 29</t>
   </si>
   <si>
     <t>AASR: 0.02
 V1: 75 V2: 57 Vties: 10</t>
   </si>
   <si>
-    <t>AASR: 0.00
-V1: 67 V2: 40 Vties: 32</t>
-  </si>
-  <si>
-    <t>AASR: 0.02
-V1: 66 V2: 47 Vties: 29</t>
+    <t>AASR: 0.27
+V1: 123 V2: 15 Vties: 4</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 117 V2: 13 Vties: 12</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 115 V2: 12 Vties: 15</t>
+  </si>
+  <si>
+    <t>AASR: 0.30
+V1: 41 V2: 43 Vties: 58</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 124 V2: 12 Vties: 6</t>
   </si>
   <si>
     <t>AASR: 0.05
@@ -640,55 +1010,55 @@
   </si>
   <si>
     <t>AASR: 0.00
-V1: 115 V2: 12 Vties: 15</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 117 V2: 13 Vties: 12</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 128 V2: 7 Vties: 7</t>
+V1: 121 V2: 3 Vties: 15</t>
   </si>
   <si>
     <t>AASR: 0.14
 V1: 88 V2: 21 Vties: 33</t>
   </si>
   <si>
-    <t>AASR: 0.27
-V1: 123 V2: 15 Vties: 4</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 124 V2: 12 Vties: 6</t>
-  </si>
-  <si>
-    <t>AASR: 0.30
-V1: 41 V2: 43 Vties: 58</t>
+    <t>AASR: 0.00
+V1: 128 V2: 7 Vties: 7</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 125 V2: 6 Vties: 11</t>
   </si>
   <si>
     <t>AASR: 0.08
 V1: 128 V2: 12 Vties: 2</t>
   </si>
   <si>
-    <t>AASR: 0.00
-V1: 121 V2: 3 Vties: 15</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 125 V2: 6 Vties: 11</t>
+    <t>AASR: 0.12
+V1: 89 V2: 32 Vties: 21</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 87 V2: 35 Vties: 20</t>
+  </si>
+  <si>
+    <t>AASR: 0.03
+V1: 77 V2: 34 Vties: 31</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 92 V2: 43 Vties: 7</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 95 V2: 33 Vties: 14</t>
   </si>
   <si>
     <t>AASR: 0.04
 V1: 62 V2: 46 Vties: 21</t>
   </si>
   <si>
-    <t>AASR: 0.03
-V1: 77 V2: 34 Vties: 31</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 87 V2: 35 Vties: 20</t>
+    <t>AASR: 0.05
+V1: 70 V2: 19 Vties: 52</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 39 V2: 26 Vties: 77</t>
   </si>
   <si>
     <t>AASR: 0.04
@@ -696,31 +1066,31 @@
   </si>
   <si>
     <t>AASR: 0.00
-V1: 39 V2: 26 Vties: 77</t>
-  </si>
-  <si>
-    <t>AASR: 0.12
-V1: 89 V2: 32 Vties: 21</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 95 V2: 33 Vties: 14</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 92 V2: 43 Vties: 7</t>
+V1: 79 V2: 28 Vties: 35</t>
   </si>
   <si>
     <t>AASR: 0.02
 V1: 84 V2: 43 Vties: 15</t>
   </si>
   <si>
-    <t>AASR: 0.05
-V1: 70 V2: 19 Vties: 52</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 79 V2: 28 Vties: 35</t>
+    <t>AASR: 0.38
+V1: 125 V2: 8 Vties: 9</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 101 V2: 1 Vties: 40</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 107 V2: 2 Vties: 33</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 140 V2: 1 Vties: 1</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 130 V2: 2 Vties: 10</t>
   </si>
   <si>
     <t>AASR: 0.27
@@ -728,131 +1098,475 @@
   </si>
   <si>
     <t>AASR: 0.00
-V1: 107 V2: 2 Vties: 33</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 101 V2: 1 Vties: 40</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 136 V2: 1 Vties: 5</t>
+V1: 141 V2: 1 Vties: 0</t>
   </si>
   <si>
     <t>AASR: 0.19
 V1: 61 V2: 26 Vties: 54</t>
   </si>
   <si>
-    <t>AASR: 0.38
+    <t>AASR: 0.00
+V1: 136 V2: 1 Vties: 5</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 139 V2: 0 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR: 0.00
+V1: 139 V2: 2 Vties: 0</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 135 V2: 5 Vties: 2</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 129 V2: 6 Vties: 7</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 123 V2: 7 Vties: 12</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.11
+V1: 133 V2: 6 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 134 V2: 5 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.23
+V1: 107 V2: 13 Vties: 13</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 127 V2: 2 Vties: 12</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.17
+V1: 107 V2: 11 Vties: 24</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 133 V2: 4 Vties: 5</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.12
+V1: 133 V2: 5 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.07
+V1: 88 V2: 31 Vties: 23</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.02
+V1: 85 V2: 33 Vties: 24</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.07
+V1: 41 V2: 57 Vties: 44</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 94 V2: 36 Vties: 12</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.05
+V1: 98 V2: 36 Vties: 8</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.05
+V1: 79 V2: 39 Vties: 22</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.05
+V1: 76 V2: 22 Vties: 41</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.14
+V1: 71 V2: 21 Vties: 50</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.02
+V1: 82 V2: 30 Vties: 26</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 90 V2: 26 Vties: 26</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.07
+V1: 96 V2: 37 Vties: 9</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.19
+V1: 90 V2: 36 Vties: 16</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 96 V2: 30 Vties: 16</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 73 V2: 35 Vties: 34</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.07
+V1: 112 V2: 23 Vties: 7</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.03
+V1: 107 V2: 24 Vties: 11</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.19
+V1: 74 V2: 25 Vties: 34</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 85 V2: 13 Vties: 42</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.09
+V1: 65 V2: 34 Vties: 43</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 96 V2: 23 Vties: 23</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.03
+V1: 102 V2: 14 Vties: 26</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.08
+V1: 103 V2: 23 Vties: 15</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.50
+V1: 140 V2: 1 Vties: 1</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 136 V2: 3 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 141 V2: 0 Vties: 1</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 138 V2: 1 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.36
+V1: 126 V2: 7 Vties: 7</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.13
+V1: 111 V2: 14 Vties: 17</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 140 V2: 0 Vties: 2</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 142 V2: 0 Vties: 0</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.50
+V1: 140 V2: 0 Vties: 2</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.07
+V1: 60 V2: 68 Vties: 14</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 61 V2: 65 Vties: 16</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.01
+V1: 28 V2: 83 Vties: 31</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 78 V2: 58 Vties: 6</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.01
+V1: 51 V2: 70 Vties: 21</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.07
+V1: 49 V2: 69 Vties: 17</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.01
+V1: 67 V2: 40 Vties: 32</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.06
+V1: 47 V2: 50 Vties: 45</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 59 V2: 64 Vties: 17</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.03
+V1: 66 V2: 47 Vties: 29</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.04
+V1: 75 V2: 57 Vties: 10</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.21
+V1: 123 V2: 15 Vties: 4</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 117 V2: 13 Vties: 12</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 115 V2: 12 Vties: 15</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.31
+V1: 41 V2: 43 Vties: 58</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 124 V2: 12 Vties: 6</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.13
+V1: 99 V2: 21 Vties: 17</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.11
+V1: 121 V2: 3 Vties: 15</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.13
+V1: 88 V2: 21 Vties: 33</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 128 V2: 7 Vties: 7</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 125 V2: 6 Vties: 11</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.14
+V1: 128 V2: 12 Vties: 2</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.21
+V1: 89 V2: 32 Vties: 21</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.02
+V1: 87 V2: 35 Vties: 20</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.05
+V1: 77 V2: 34 Vties: 31</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.04
+V1: 92 V2: 43 Vties: 7</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.04
+V1: 95 V2: 33 Vties: 14</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.06
+V1: 62 V2: 46 Vties: 21</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.08
+V1: 70 V2: 19 Vties: 52</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.04
+V1: 39 V2: 26 Vties: 77</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.02
+V1: 94 V2: 24 Vties: 20</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.03
+V1: 79 V2: 28 Vties: 35</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.07
+V1: 84 V2: 43 Vties: 15</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.29
 V1: 125 V2: 8 Vties: 9</t>
   </si>
   <si>
-    <t>AASR: 0.00
+    <t>AASR_WITH_TIES: 0.02
+V1: 101 V2: 1 Vties: 40</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.11
+V1: 107 V2: 2 Vties: 33</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 140 V2: 1 Vties: 1</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
 V1: 130 V2: 2 Vties: 10</t>
   </si>
   <si>
-    <t>AASR: 0.00
-V1: 140 V2: 1 Vties: 1</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
+    <t>AASR_WITH_TIES: 0.20
+V1: 101 V2: 11 Vties: 24</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 141 V2: 1 Vties: 0</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.10
+V1: 61 V2: 26 Vties: 54</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 136 V2: 1 Vties: 5</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
+V1: 139 V2: 0 Vties: 3</t>
+  </si>
+  <si>
+    <t>AASR_WITH_TIES: 0.00
 V1: 139 V2: 2 Vties: 0</t>
   </si>
   <si>
-    <t>AASR: 0.00
-V1: 141 V2: 1 Vties: 0</t>
-  </si>
-  <si>
-    <t>AASR: 0.00
-V1: 139 V2: 0 Vties: 3</t>
+    <t>FR: 0.08
+V1: 135 V2: 5 Vties: 2</t>
+  </si>
+  <si>
+    <t>FR: 0.27
+V1: 129 V2: 6 Vties: 7</t>
+  </si>
+  <si>
+    <t>FR: 0.17
+V1: 123 V2: 7 Vties: 12</t>
+  </si>
+  <si>
+    <t>FR: 0.11
+V1: 133 V2: 6 Vties: 3</t>
+  </si>
+  <si>
+    <t>FR: 0.26
+V1: 134 V2: 5 Vties: 3</t>
   </si>
   <si>
     <t>FR: 0.37
 V1: 107 V2: 13 Vties: 13</t>
   </si>
   <si>
-    <t>FR: 0.17
-V1: 123 V2: 7 Vties: 12</t>
-  </si>
-  <si>
-    <t>FR: 0.27
-V1: 129 V2: 6 Vties: 7</t>
+    <t>FR: 0.12
+V1: 127 V2: 2 Vties: 12</t>
+  </si>
+  <si>
+    <t>FR: 0.46
+V1: 107 V2: 11 Vties: 24</t>
   </si>
   <si>
     <t>FR: 0.13
 V1: 133 V2: 3 Vties: 6</t>
   </si>
   <si>
-    <t>FR: 0.46
-V1: 107 V2: 11 Vties: 24</t>
-  </si>
-  <si>
     <t>FR: 0.08
-V1: 135 V2: 5 Vties: 2</t>
-  </si>
-  <si>
-    <t>FR: 0.26
-V1: 134 V2: 5 Vties: 3</t>
-  </si>
-  <si>
-    <t>FR: 0.11
-V1: 133 V2: 6 Vties: 3</t>
+V1: 133 V2: 4 Vties: 5</t>
   </si>
   <si>
     <t>FR: 0.13
 V1: 133 V2: 5 Vties: 3</t>
   </si>
   <si>
-    <t>FR: 0.12
-V1: 127 V2: 2 Vties: 12</t>
-  </si>
-  <si>
-    <t>FR: 0.08
-V1: 133 V2: 4 Vties: 5</t>
+    <t>FR: 0.35
+V1: 88 V2: 31 Vties: 23</t>
+  </si>
+  <si>
+    <t>FR: 0.47
+V1: 85 V2: 33 Vties: 24</t>
+  </si>
+  <si>
+    <t>FR: 0.42
+V1: 41 V2: 57 Vties: 44</t>
+  </si>
+  <si>
+    <t>FR: 0.23
+V1: 94 V2: 36 Vties: 12</t>
+  </si>
+  <si>
+    <t>FR: 0.40
+V1: 98 V2: 36 Vties: 8</t>
   </si>
   <si>
     <t>FR: 0.45
 V1: 79 V2: 39 Vties: 22</t>
   </si>
   <si>
-    <t>FR: 0.42
-V1: 41 V2: 57 Vties: 44</t>
-  </si>
-  <si>
-    <t>FR: 0.47
-V1: 85 V2: 33 Vties: 24</t>
+    <t>FR: 0.36
+V1: 76 V2: 22 Vties: 41</t>
+  </si>
+  <si>
+    <t>FR: 0.58
+V1: 71 V2: 21 Vties: 50</t>
   </si>
   <si>
     <t>FR: 0.27
 V1: 82 V2: 30 Vties: 26</t>
   </si>
   <si>
-    <t>FR: 0.58
-V1: 71 V2: 21 Vties: 50</t>
-  </si>
-  <si>
-    <t>FR: 0.35
-V1: 88 V2: 31 Vties: 23</t>
-  </si>
-  <si>
-    <t>FR: 0.40
-V1: 98 V2: 36 Vties: 8</t>
-  </si>
-  <si>
-    <t>FR: 0.23
-V1: 94 V2: 36 Vties: 12</t>
+    <t>FR: 0.25
+V1: 90 V2: 26 Vties: 26</t>
   </si>
   <si>
     <t>FR: 0.23
 V1: 96 V2: 37 Vties: 9</t>
   </si>
   <si>
-    <t>FR: 0.36
-V1: 76 V2: 22 Vties: 41</t>
+    <t>FR: 0.32
+V1: 90 V2: 36 Vties: 16</t>
+  </si>
+  <si>
+    <t>FR: 0.42
+V1: 96 V2: 30 Vties: 16</t>
+  </si>
+  <si>
+    <t>FR: 0.38
+V1: 73 V2: 35 Vties: 34</t>
   </si>
   <si>
     <t>FR: 0.25
-V1: 90 V2: 26 Vties: 26</t>
+V1: 112 V2: 23 Vties: 7</t>
+  </si>
+  <si>
+    <t>FR: 0.49
+V1: 107 V2: 24 Vties: 11</t>
   </si>
   <si>
     <t>FR: 0.57
@@ -860,611 +1574,591 @@
   </si>
   <si>
     <t>FR: 0.38
-V1: 73 V2: 35 Vties: 34</t>
-  </si>
-  <si>
-    <t>FR: 0.42
-V1: 96 V2: 30 Vties: 16</t>
+V1: 85 V2: 13 Vties: 42</t>
+  </si>
+  <si>
+    <t>FR: 0.62
+V1: 65 V2: 34 Vties: 43</t>
   </si>
   <si>
     <t>FR: 0.31
 V1: 96 V2: 23 Vties: 23</t>
   </si>
   <si>
-    <t>FR: 0.62
-V1: 65 V2: 34 Vties: 43</t>
-  </si>
-  <si>
-    <t>FR: 0.32
-V1: 90 V2: 36 Vties: 16</t>
-  </si>
-  <si>
-    <t>FR: 0.49
-V1: 107 V2: 24 Vties: 11</t>
-  </si>
-  <si>
-    <t>FR: 0.25
-V1: 112 V2: 23 Vties: 7</t>
+    <t>FR: 0.31
+V1: 102 V2: 14 Vties: 26</t>
   </si>
   <si>
     <t>FR: 0.28
 V1: 103 V2: 23 Vties: 15</t>
   </si>
   <si>
-    <t>FR: 0.38
-V1: 85 V2: 13 Vties: 42</t>
-  </si>
-  <si>
-    <t>FR: 0.31
-V1: 102 V2: 14 Vties: 26</t>
+    <t>FR: 0.04
+V1: 140 V2: 1 Vties: 1</t>
+  </si>
+  <si>
+    <t>FR: 0.08
+V1: 136 V2: 3 Vties: 3</t>
+  </si>
+  <si>
+    <t>FR: 0.09
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
+    <t>FR: 0.02
+V1: 141 V2: 0 Vties: 1</t>
+  </si>
+  <si>
+    <t>FR: 0.08
+V1: 138 V2: 1 Vties: 3</t>
   </si>
   <si>
     <t>FR: 0.22
 V1: 126 V2: 7 Vties: 7</t>
   </si>
   <si>
-    <t>FR: 0.09
-V1: 133 V2: 3 Vties: 6</t>
-  </si>
-  <si>
-    <t>FR: 0.08
-V1: 136 V2: 3 Vties: 3</t>
+    <t>FR: 0.01
+V1: 141 V2: 0 Vties: 1</t>
+  </si>
+  <si>
+    <t>FR: 0.29
+V1: 111 V2: 14 Vties: 17</t>
   </si>
   <si>
     <t>FR: 0.02
 V1: 140 V2: 0 Vties: 2</t>
   </si>
   <si>
-    <t>FR: 0.29
-V1: 111 V2: 14 Vties: 17</t>
-  </si>
-  <si>
-    <t>FR: 0.04
-V1: 140 V2: 1 Vties: 1</t>
-  </si>
-  <si>
-    <t>FR: 0.08
-V1: 138 V2: 1 Vties: 3</t>
-  </si>
-  <si>
-    <t>FR: 0.02
-V1: 141 V2: 0 Vties: 1</t>
+    <t>FR: 0.01
+V1: 142 V2: 0 Vties: 0</t>
   </si>
   <si>
     <t>FR: 0.03
 V1: 140 V2: 0 Vties: 2</t>
   </si>
   <si>
-    <t>FR: 0.01
-V1: 141 V2: 0 Vties: 1</t>
-  </si>
-  <si>
-    <t>FR: 0.01
-V1: 142 V2: 0 Vties: 0</t>
+    <t>FR: 0.27
+V1: 60 V2: 68 Vties: 14</t>
+  </si>
+  <si>
+    <t>FR: 0.28
+V1: 61 V2: 65 Vties: 16</t>
+  </si>
+  <si>
+    <t>FR: 0.25
+V1: 28 V2: 83 Vties: 31</t>
+  </si>
+  <si>
+    <t>FR: 0.14
+V1: 78 V2: 58 Vties: 6</t>
+  </si>
+  <si>
+    <t>FR: 0.36
+V1: 51 V2: 70 Vties: 21</t>
   </si>
   <si>
     <t>FR: 0.38
 V1: 49 V2: 69 Vties: 17</t>
   </si>
   <si>
-    <t>FR: 0.25
-V1: 28 V2: 83 Vties: 31</t>
-  </si>
-  <si>
-    <t>FR: 0.28
-V1: 61 V2: 65 Vties: 16</t>
+    <t>FR: 0.29
+V1: 67 V2: 40 Vties: 32</t>
+  </si>
+  <si>
+    <t>FR: 0.53
+V1: 47 V2: 50 Vties: 45</t>
   </si>
   <si>
     <t>FR: 0.21
 V1: 59 V2: 64 Vties: 17</t>
   </si>
   <si>
-    <t>FR: 0.53
-V1: 47 V2: 50 Vties: 45</t>
-  </si>
-  <si>
-    <t>FR: 0.27
-V1: 60 V2: 68 Vties: 14</t>
-  </si>
-  <si>
-    <t>FR: 0.36
-V1: 51 V2: 70 Vties: 21</t>
-  </si>
-  <si>
-    <t>FR: 0.14
-V1: 78 V2: 58 Vties: 6</t>
+    <t>FR: 0.30
+V1: 66 V2: 47 Vties: 29</t>
   </si>
   <si>
     <t>FR: 0.24
 V1: 75 V2: 57 Vties: 10</t>
   </si>
   <si>
-    <t>FR: 0.29
-V1: 67 V2: 40 Vties: 32</t>
-  </si>
-  <si>
-    <t>FR: 0.30
-V1: 66 V2: 47 Vties: 29</t>
+    <t>FR: 0.21
+V1: 123 V2: 15 Vties: 4</t>
+  </si>
+  <si>
+    <t>FR: 0.32
+V1: 117 V2: 13 Vties: 12</t>
+  </si>
+  <si>
+    <t>FR: 0.20
+V1: 115 V2: 12 Vties: 15</t>
+  </si>
+  <si>
+    <t>FR: 0.58
+V1: 41 V2: 43 Vties: 58</t>
+  </si>
+  <si>
+    <t>FR: 0.43
+V1: 124 V2: 12 Vties: 6</t>
   </si>
   <si>
     <t>FR: 0.42
 V1: 99 V2: 21 Vties: 17</t>
   </si>
   <si>
-    <t>FR: 0.20
-V1: 115 V2: 12 Vties: 15</t>
-  </si>
-  <si>
-    <t>FR: 0.32
-V1: 117 V2: 13 Vties: 12</t>
+    <t>FR: 0.14
+V1: 121 V2: 3 Vties: 15</t>
+  </si>
+  <si>
+    <t>FR: 0.49
+V1: 88 V2: 21 Vties: 33</t>
   </si>
   <si>
     <t>FR: 0.15
 V1: 128 V2: 7 Vties: 7</t>
   </si>
   <si>
-    <t>FR: 0.49
-V1: 88 V2: 21 Vties: 33</t>
-  </si>
-  <si>
-    <t>FR: 0.21
-V1: 123 V2: 15 Vties: 4</t>
-  </si>
-  <si>
-    <t>FR: 0.43
-V1: 124 V2: 12 Vties: 6</t>
-  </si>
-  <si>
-    <t>FR: 0.58
-V1: 41 V2: 43 Vties: 58</t>
+    <t>FR: 0.12
+V1: 125 V2: 6 Vties: 11</t>
   </si>
   <si>
     <t>FR: 0.13
 V1: 128 V2: 12 Vties: 2</t>
   </si>
   <si>
-    <t>FR: 0.14
-V1: 121 V2: 3 Vties: 15</t>
-  </si>
-  <si>
-    <t>FR: 0.12
-V1: 125 V2: 6 Vties: 11</t>
+    <t>FR: 0.37
+V1: 89 V2: 32 Vties: 21</t>
+  </si>
+  <si>
+    <t>FR: 0.55
+V1: 87 V2: 35 Vties: 20</t>
+  </si>
+  <si>
+    <t>FR: 0.37
+V1: 77 V2: 34 Vties: 31</t>
+  </si>
+  <si>
+    <t>FR: 0.24
+V1: 92 V2: 43 Vties: 7</t>
+  </si>
+  <si>
+    <t>FR: 0.63
+V1: 95 V2: 33 Vties: 14</t>
   </si>
   <si>
     <t>FR: 0.49
 V1: 62 V2: 46 Vties: 21</t>
   </si>
   <si>
-    <t>FR: 0.37
-V1: 77 V2: 34 Vties: 31</t>
-  </si>
-  <si>
-    <t>FR: 0.55
-V1: 87 V2: 35 Vties: 20</t>
+    <t>FR: 0.46
+V1: 70 V2: 19 Vties: 52</t>
+  </si>
+  <si>
+    <t>FR: 0.65
+V1: 39 V2: 26 Vties: 77</t>
   </si>
   <si>
     <t>FR: 0.37
 V1: 94 V2: 24 Vties: 20</t>
   </si>
   <si>
-    <t>FR: 0.65
-V1: 39 V2: 26 Vties: 77</t>
-  </si>
-  <si>
-    <t>FR: 0.37
-V1: 89 V2: 32 Vties: 21</t>
-  </si>
-  <si>
-    <t>FR: 0.63
-V1: 95 V2: 33 Vties: 14</t>
-  </si>
-  <si>
-    <t>FR: 0.24
-V1: 92 V2: 43 Vties: 7</t>
+    <t>FR: 0.38
+V1: 79 V2: 28 Vties: 35</t>
   </si>
   <si>
     <t>FR: 0.30
 V1: 84 V2: 43 Vties: 15</t>
   </si>
   <si>
-    <t>FR: 0.46
-V1: 70 V2: 19 Vties: 52</t>
-  </si>
-  <si>
-    <t>FR: 0.38
-V1: 79 V2: 28 Vties: 35</t>
+    <t>FR: 0.37
+V1: 125 V2: 8 Vties: 9</t>
+  </si>
+  <si>
+    <t>FR: 0.57
+V1: 101 V2: 1 Vties: 40</t>
+  </si>
+  <si>
+    <t>FR: 0.44
+V1: 107 V2: 2 Vties: 33</t>
+  </si>
+  <si>
+    <t>FR: 0.10
+V1: 140 V2: 1 Vties: 1</t>
+  </si>
+  <si>
+    <t>FR: 0.57
+V1: 130 V2: 2 Vties: 10</t>
   </si>
   <si>
     <t>FR: 0.62
 V1: 101 V2: 11 Vties: 24</t>
   </si>
   <si>
-    <t>FR: 0.44
-V1: 107 V2: 2 Vties: 33</t>
-  </si>
-  <si>
-    <t>FR: 0.57
-V1: 101 V2: 1 Vties: 40</t>
+    <t>FR: 0.04
+V1: 141 V2: 1 Vties: 0</t>
+  </si>
+  <si>
+    <t>FR: 0.65
+V1: 61 V2: 26 Vties: 54</t>
   </si>
   <si>
     <t>FR: 0.30
 V1: 136 V2: 1 Vties: 5</t>
   </si>
   <si>
-    <t>FR: 0.65
-V1: 61 V2: 26 Vties: 54</t>
-  </si>
-  <si>
-    <t>FR: 0.37
-V1: 125 V2: 8 Vties: 9</t>
-  </si>
-  <si>
-    <t>FR: 0.57
-V1: 130 V2: 2 Vties: 10</t>
-  </si>
-  <si>
-    <t>FR: 0.10
-V1: 140 V2: 1 Vties: 1</t>
+    <t>FR: 0.08
+V1: 139 V2: 0 Vties: 3</t>
   </si>
   <si>
     <t>FR: 0.16
 V1: 139 V2: 2 Vties: 0</t>
   </si>
   <si>
-    <t>FR: 0.04
-V1: 141 V2: 1 Vties: 0</t>
-  </si>
-  <si>
-    <t>FR: 0.08
-V1: 139 V2: 0 Vties: 3</t>
+    <t>CR: 0.93
+V1: 135 V2: 5 Vties: 2</t>
+  </si>
+  <si>
+    <t>CR: 0.77
+V1: 129 V2: 6 Vties: 7</t>
+  </si>
+  <si>
+    <t>CR: 0.91
+V1: 123 V2: 7 Vties: 12</t>
+  </si>
+  <si>
+    <t>CR: 0.91
+V1: 133 V2: 6 Vties: 3</t>
+  </si>
+  <si>
+    <t>CR: 0.76
+V1: 134 V2: 5 Vties: 3</t>
   </si>
   <si>
     <t>CR: 0.70
 V1: 107 V2: 13 Vties: 13</t>
   </si>
   <si>
-    <t>CR: 0.91
-V1: 123 V2: 7 Vties: 12</t>
-  </si>
-  <si>
-    <t>CR: 0.77
-V1: 129 V2: 6 Vties: 7</t>
+    <t>CR: 0.96
+V1: 127 V2: 2 Vties: 12</t>
+  </si>
+  <si>
+    <t>CR: 0.64
+V1: 107 V2: 11 Vties: 24</t>
   </si>
   <si>
     <t>CR: 0.91
 V1: 133 V2: 3 Vties: 6</t>
   </si>
   <si>
-    <t>CR: 0.64
-V1: 107 V2: 11 Vties: 24</t>
-  </si>
-  <si>
-    <t>CR: 0.93
-V1: 135 V2: 5 Vties: 2</t>
-  </si>
-  <si>
-    <t>CR: 0.76
-V1: 134 V2: 5 Vties: 3</t>
-  </si>
-  <si>
-    <t>CR: 0.91
-V1: 133 V2: 6 Vties: 3</t>
+    <t>CR: 0.96
+V1: 133 V2: 4 Vties: 5</t>
   </si>
   <si>
     <t>CR: 0.88
 V1: 133 V2: 5 Vties: 3</t>
   </si>
   <si>
-    <t>CR: 0.96
-V1: 127 V2: 2 Vties: 12</t>
-  </si>
-  <si>
-    <t>CR: 0.96
-V1: 133 V2: 4 Vties: 5</t>
+    <t>CR: 0.77
+V1: 88 V2: 31 Vties: 23</t>
+  </si>
+  <si>
+    <t>CR: 0.64
+V1: 85 V2: 33 Vties: 24</t>
+  </si>
+  <si>
+    <t>CR: 0.84
+V1: 41 V2: 57 Vties: 44</t>
+  </si>
+  <si>
+    <t>CR: 0.84
+V1: 94 V2: 36 Vties: 12</t>
+  </si>
+  <si>
+    <t>CR: 0.63
+V1: 98 V2: 36 Vties: 8</t>
   </si>
   <si>
     <t>CR: 0.65
 V1: 79 V2: 39 Vties: 22</t>
   </si>
   <si>
-    <t>CR: 0.84
-V1: 41 V2: 57 Vties: 44</t>
+    <t>CR: 0.91
+V1: 76 V2: 22 Vties: 41</t>
   </si>
   <si>
     <t>CR: 0.64
-V1: 85 V2: 33 Vties: 24</t>
+V1: 71 V2: 21 Vties: 50</t>
   </si>
   <si>
     <t>CR: 0.90
 V1: 82 V2: 30 Vties: 26</t>
   </si>
   <si>
-    <t>CR: 0.64
-V1: 71 V2: 21 Vties: 50</t>
-  </si>
-  <si>
-    <t>CR: 0.77
-V1: 88 V2: 31 Vties: 23</t>
-  </si>
-  <si>
-    <t>CR: 0.63
-V1: 98 V2: 36 Vties: 8</t>
-  </si>
-  <si>
-    <t>CR: 0.84
-V1: 94 V2: 36 Vties: 12</t>
+    <t>CR: 0.92
+V1: 90 V2: 26 Vties: 26</t>
   </si>
   <si>
     <t>CR: 0.82
 V1: 96 V2: 37 Vties: 9</t>
   </si>
   <si>
-    <t>CR: 0.91
-V1: 76 V2: 22 Vties: 41</t>
-  </si>
-  <si>
-    <t>CR: 0.92
-V1: 90 V2: 26 Vties: 26</t>
+    <t>CR: 0.76
+V1: 90 V2: 36 Vties: 16</t>
+  </si>
+  <si>
+    <t>CR: 0.65
+V1: 96 V2: 30 Vties: 16</t>
+  </si>
+  <si>
+    <t>CR: 0.81
+V1: 73 V2: 35 Vties: 34</t>
+  </si>
+  <si>
+    <t>CR: 0.79
+V1: 112 V2: 23 Vties: 7</t>
+  </si>
+  <si>
+    <t>CR: 0.55
+V1: 107 V2: 24 Vties: 11</t>
   </si>
   <si>
     <t>CR: 0.58
 V1: 74 V2: 25 Vties: 34</t>
   </si>
   <si>
-    <t>CR: 0.81
-V1: 73 V2: 35 Vties: 34</t>
-  </si>
-  <si>
-    <t>CR: 0.65
-V1: 96 V2: 30 Vties: 16</t>
+    <t>CR: 0.89
+V1: 85 V2: 13 Vties: 42</t>
+  </si>
+  <si>
+    <t>CR: 0.55
+V1: 65 V2: 34 Vties: 43</t>
   </si>
   <si>
     <t>CR: 0.82
 V1: 96 V2: 23 Vties: 23</t>
   </si>
   <si>
-    <t>CR: 0.55
-V1: 65 V2: 34 Vties: 43</t>
-  </si>
-  <si>
-    <t>CR: 0.76
-V1: 90 V2: 36 Vties: 16</t>
-  </si>
-  <si>
-    <t>CR: 0.55
-V1: 107 V2: 24 Vties: 11</t>
-  </si>
-  <si>
-    <t>CR: 0.79
-V1: 112 V2: 23 Vties: 7</t>
+    <t>CR: 0.84
+V1: 102 V2: 14 Vties: 26</t>
   </si>
   <si>
     <t>CR: 0.81
 V1: 103 V2: 23 Vties: 15</t>
   </si>
   <si>
-    <t>CR: 0.89
-V1: 85 V2: 13 Vties: 42</t>
-  </si>
-  <si>
-    <t>CR: 0.84
-V1: 102 V2: 14 Vties: 26</t>
+    <t>CR: 0.97
+V1: 140 V2: 1 Vties: 1</t>
+  </si>
+  <si>
+    <t>CR: 0.94
+V1: 136 V2: 3 Vties: 3</t>
+  </si>
+  <si>
+    <t>CR: 0.95
+V1: 133 V2: 3 Vties: 6</t>
+  </si>
+  <si>
+    <t>CR: 0.99
+V1: 141 V2: 0 Vties: 1</t>
+  </si>
+  <si>
+    <t>CR: 0.94
+V1: 138 V2: 1 Vties: 3</t>
   </si>
   <si>
     <t>CR: 0.82
 V1: 126 V2: 7 Vties: 7</t>
   </si>
   <si>
-    <t>CR: 0.95
-V1: 133 V2: 3 Vties: 6</t>
-  </si>
-  <si>
-    <t>CR: 0.94
-V1: 136 V2: 3 Vties: 3</t>
+    <t>CR: 1.00
+V1: 141 V2: 0 Vties: 1</t>
+  </si>
+  <si>
+    <t>CR: 0.81
+V1: 111 V2: 14 Vties: 17</t>
   </si>
   <si>
     <t>CR: 0.99
 V1: 140 V2: 0 Vties: 2</t>
   </si>
   <si>
-    <t>CR: 0.81
-V1: 111 V2: 14 Vties: 17</t>
-  </si>
-  <si>
-    <t>CR: 0.97
-V1: 140 V2: 1 Vties: 1</t>
-  </si>
-  <si>
-    <t>CR: 0.94
-V1: 138 V2: 1 Vties: 3</t>
-  </si>
-  <si>
-    <t>CR: 0.99
-V1: 141 V2: 0 Vties: 1</t>
-  </si>
-  <si>
-    <t>CR: 1.00
-V1: 141 V2: 0 Vties: 1</t>
-  </si>
-  <si>
     <t>CR: 0.99
 V1: 142 V2: 0 Vties: 0</t>
   </si>
   <si>
+    <t>CR: 0.80
+V1: 60 V2: 68 Vties: 14</t>
+  </si>
+  <si>
+    <t>CR: 0.81
+V1: 61 V2: 65 Vties: 16</t>
+  </si>
+  <si>
+    <t>CR: 0.95
+V1: 28 V2: 83 Vties: 31</t>
+  </si>
+  <si>
+    <t>CR: 0.90
+V1: 78 V2: 58 Vties: 6</t>
+  </si>
+  <si>
+    <t>CR: 0.75
+V1: 51 V2: 70 Vties: 21</t>
+  </si>
+  <si>
     <t>CR: 0.71
 V1: 49 V2: 69 Vties: 17</t>
   </si>
   <si>
-    <t>CR: 0.95
-V1: 28 V2: 83 Vties: 31</t>
-  </si>
-  <si>
-    <t>CR: 0.81
-V1: 61 V2: 65 Vties: 16</t>
+    <t>CR: 0.92
+V1: 67 V2: 40 Vties: 32</t>
+  </si>
+  <si>
+    <t>CR: 0.69
+V1: 47 V2: 50 Vties: 45</t>
   </si>
   <si>
     <t>CR: 0.90
 V1: 59 V2: 64 Vties: 17</t>
   </si>
   <si>
-    <t>CR: 0.69
-V1: 47 V2: 50 Vties: 45</t>
-  </si>
-  <si>
-    <t>CR: 0.80
-V1: 60 V2: 68 Vties: 14</t>
-  </si>
-  <si>
-    <t>CR: 0.75
-V1: 51 V2: 70 Vties: 21</t>
-  </si>
-  <si>
-    <t>CR: 0.90
-V1: 78 V2: 58 Vties: 6</t>
+    <t>CR: 0.88
+V1: 66 V2: 47 Vties: 29</t>
   </si>
   <si>
     <t>CR: 0.82
 V1: 75 V2: 57 Vties: 10</t>
   </si>
   <si>
-    <t>CR: 0.92
-V1: 67 V2: 40 Vties: 32</t>
-  </si>
-  <si>
-    <t>CR: 0.88
-V1: 66 V2: 47 Vties: 29</t>
+    <t>CR: 0.81
+V1: 123 V2: 15 Vties: 4</t>
+  </si>
+  <si>
+    <t>CR: 0.75
+V1: 117 V2: 13 Vties: 12</t>
+  </si>
+  <si>
+    <t>CR: 0.90
+V1: 115 V2: 12 Vties: 15</t>
+  </si>
+  <si>
+    <t>CR: 0.71
+V1: 41 V2: 43 Vties: 58</t>
+  </si>
+  <si>
+    <t>CR: 0.60
+V1: 124 V2: 12 Vties: 6</t>
   </si>
   <si>
     <t>CR: 0.66
 V1: 99 V2: 21 Vties: 17</t>
   </si>
   <si>
-    <t>CR: 0.90
-V1: 115 V2: 12 Vties: 15</t>
-  </si>
-  <si>
-    <t>CR: 0.75
-V1: 117 V2: 13 Vties: 12</t>
+    <t>CR: 0.96
+V1: 121 V2: 3 Vties: 15</t>
+  </si>
+  <si>
+    <t>CR: 0.67
+V1: 88 V2: 21 Vties: 33</t>
   </si>
   <si>
     <t>CR: 0.89
 V1: 128 V2: 7 Vties: 7</t>
   </si>
   <si>
-    <t>CR: 0.67
-V1: 88 V2: 21 Vties: 33</t>
-  </si>
-  <si>
-    <t>CR: 0.81
-V1: 123 V2: 15 Vties: 4</t>
-  </si>
-  <si>
-    <t>CR: 0.60
-V1: 124 V2: 12 Vties: 6</t>
-  </si>
-  <si>
-    <t>CR: 0.71
-V1: 41 V2: 43 Vties: 58</t>
+    <t>CR: 0.95
+V1: 125 V2: 6 Vties: 11</t>
   </si>
   <si>
     <t>CR: 0.88
 V1: 128 V2: 12 Vties: 2</t>
   </si>
   <si>
-    <t>CR: 0.96
-V1: 121 V2: 3 Vties: 15</t>
-  </si>
-  <si>
-    <t>CR: 0.95
-V1: 125 V2: 6 Vties: 11</t>
+    <t>CR: 0.74
+V1: 89 V2: 32 Vties: 21</t>
+  </si>
+  <si>
+    <t>CR: 0.52
+V1: 87 V2: 35 Vties: 20</t>
+  </si>
+  <si>
+    <t>CR: 0.81
+V1: 77 V2: 34 Vties: 31</t>
+  </si>
+  <si>
+    <t>CR: 0.80
+V1: 92 V2: 43 Vties: 7</t>
+  </si>
+  <si>
+    <t>CR: 0.41
+V1: 95 V2: 33 Vties: 14</t>
   </si>
   <si>
     <t>CR: 0.61
 V1: 62 V2: 46 Vties: 21</t>
   </si>
   <si>
-    <t>CR: 0.81
-V1: 77 V2: 34 Vties: 31</t>
-  </si>
-  <si>
-    <t>CR: 0.52
-V1: 87 V2: 35 Vties: 20</t>
+    <t>CR: 0.85
+V1: 70 V2: 19 Vties: 52</t>
+  </si>
+  <si>
+    <t>CR: 0.75
+V1: 39 V2: 26 Vties: 77</t>
   </si>
   <si>
     <t>CR: 0.74
 V1: 94 V2: 24 Vties: 20</t>
   </si>
   <si>
-    <t>CR: 0.75
-V1: 39 V2: 26 Vties: 77</t>
-  </si>
-  <si>
-    <t>CR: 0.74
-V1: 89 V2: 32 Vties: 21</t>
-  </si>
-  <si>
-    <t>CR: 0.41
-V1: 95 V2: 33 Vties: 14</t>
-  </si>
-  <si>
-    <t>CR: 0.80
-V1: 92 V2: 43 Vties: 7</t>
+    <t>CR: 0.82
+V1: 79 V2: 28 Vties: 35</t>
   </si>
   <si>
     <t>CR: 0.78
 V1: 84 V2: 43 Vties: 15</t>
   </si>
   <si>
-    <t>CR: 0.85
-V1: 70 V2: 19 Vties: 52</t>
-  </si>
-  <si>
-    <t>CR: 0.82
-V1: 79 V2: 28 Vties: 35</t>
+    <t>CR: 0.67
+V1: 125 V2: 8 Vties: 9</t>
+  </si>
+  <si>
+    <t>CR: 0.60
+V1: 101 V2: 1 Vties: 40</t>
+  </si>
+  <si>
+    <t>CR: 0.73
+V1: 107 V2: 2 Vties: 33</t>
+  </si>
+  <si>
+    <t>CR: 0.91
+V1: 140 V2: 1 Vties: 1</t>
+  </si>
+  <si>
+    <t>CR: 0.46
+V1: 130 V2: 2 Vties: 10</t>
   </si>
   <si>
     <t>CR: 0.46
 V1: 101 V2: 11 Vties: 24</t>
   </si>
   <si>
-    <t>CR: 0.73
-V1: 107 V2: 2 Vties: 33</t>
-  </si>
-  <si>
-    <t>CR: 0.60
-V1: 101 V2: 1 Vties: 40</t>
+    <t>CR: 0.96
+V1: 141 V2: 1 Vties: 0</t>
+  </si>
+  <si>
+    <t>CR: 0.56
+V1: 61 V2: 26 Vties: 54</t>
   </si>
   <si>
     <t>CR: 0.72
 V1: 136 V2: 1 Vties: 5</t>
   </si>
   <si>
-    <t>CR: 0.56
-V1: 61 V2: 26 Vties: 54</t>
-  </si>
-  <si>
-    <t>CR: 0.67
-V1: 125 V2: 8 Vties: 9</t>
-  </si>
-  <si>
-    <t>CR: 0.46
-V1: 130 V2: 2 Vties: 10</t>
-  </si>
-  <si>
-    <t>CR: 0.91
-V1: 140 V2: 1 Vties: 1</t>
+    <t>CR: 0.94
+V1: 139 V2: 0 Vties: 3</t>
   </si>
   <si>
     <t>CR: 0.84
 V1: 139 V2: 2 Vties: 0</t>
-  </si>
-  <si>
-    <t>CR: 0.96
-V1: 141 V2: 1 Vties: 0</t>
-  </si>
-  <si>
-    <t>CR: 0.94
-V1: 139 V2: 0 Vties: 3</t>
   </si>
 </sst>
 </file>
@@ -2106,7 +2800,7 @@
         <v>50</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>56</v>
+        <v>61</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>71</v>
@@ -2135,7 +2829,7 @@
         <v>51</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>72</v>
@@ -2164,7 +2858,7 @@
         <v>52</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>73</v>
@@ -2238,16 +2932,16 @@
         <v>140</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2264,19 +2958,19 @@
         <v>130</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>110</v>
+        <v>141</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2293,19 +2987,19 @@
         <v>131</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2322,19 +3016,19 @@
         <v>132</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2351,19 +3045,19 @@
         <v>133</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2380,19 +3074,19 @@
         <v>134</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2409,19 +3103,19 @@
         <v>135</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2438,19 +3132,19 @@
         <v>136</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2467,19 +3161,19 @@
         <v>137</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2496,19 +3190,19 @@
         <v>138</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2525,19 +3219,19 @@
         <v>139</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
     </row>
   </sheetData>
@@ -2587,28 +3281,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2616,28 +3310,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -2645,28 +3339,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>227</v>
+        <v>202</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -2674,28 +3368,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -2703,28 +3397,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -2732,28 +3426,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -2761,28 +3455,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -2790,28 +3484,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>232</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -2819,28 +3513,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="E10" s="1" t="s">
         <v>233</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -2848,28 +3542,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="E11" s="1" t="s">
         <v>234</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -2877,28 +3571,28 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="I12" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
     </row>
   </sheetData>
@@ -2948,28 +3642,28 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="3" spans="1:9">
@@ -2977,28 +3671,28 @@
         <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3006,28 +3700,28 @@
         <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="C4" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E4" s="1" t="s">
-        <v>315</v>
+        <v>287</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="I4" s="1" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="5" spans="1:9">
@@ -3035,28 +3729,28 @@
         <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="H5" s="1" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="I5" s="1" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3064,28 +3758,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="C6" s="1" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="H6" s="1" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="I6" s="1" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3093,28 +3787,28 @@
         <v>14</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="C7" s="1" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="H7" s="1" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="I7" s="1" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3122,28 +3816,28 @@
         <v>15</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="C8" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>319</v>
+        <v>314</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="H8" s="1" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="I8" s="1" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3151,28 +3845,28 @@
         <v>16</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="C9" s="1" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="H9" s="1" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="I9" s="1" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3180,28 +3874,28 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="H10" s="1" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="I10" s="1" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -3209,28 +3903,28 @@
         <v>18</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="C11" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="E11" s="1" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="H11" s="1" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="I11" s="1" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -3238,28 +3932,750 @@
         <v>19</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="H12" s="1" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="I12" s="1" t="s">
+        <v>364</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="10" width="20.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>365</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>387</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>409</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>366</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>388</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>410</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>421</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>367</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>389</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>400</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>411</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>422</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>433</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>368</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>379</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>390</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>434</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>369</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>380</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>391</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>402</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>435</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>392</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>403</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>436</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>382</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>393</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>404</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>437</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>383</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>394</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>405</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>438</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>384</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>395</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>428</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>439</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>385</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>407</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>440</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>386</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>408</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>441</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>452</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:J12"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="10" width="20.7109375" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>453</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>464</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>475</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>486</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>496</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>507</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>518</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>529</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
+      <c r="A3" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>454</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>465</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>476</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>487</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>497</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>508</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>519</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>455</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>466</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>477</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>488</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="G4" s="1" t="s">
+        <v>509</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>520</v>
+      </c>
+      <c r="I4" s="1" t="s">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>456</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>467</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>478</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>489</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="G5" s="1" t="s">
+        <v>510</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>521</v>
+      </c>
+      <c r="I5" s="1" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>457</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>468</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>479</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>490</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="G6" s="1" t="s">
+        <v>511</v>
+      </c>
+      <c r="H6" s="1" t="s">
+        <v>522</v>
+      </c>
+      <c r="I6" s="1" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>458</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>469</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>480</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>491</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="G7" s="1" t="s">
+        <v>512</v>
+      </c>
+      <c r="H7" s="1" t="s">
+        <v>523</v>
+      </c>
+      <c r="I7" s="1" t="s">
+        <v>534</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>459</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>470</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>481</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>492</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="G8" s="1" t="s">
+        <v>513</v>
+      </c>
+      <c r="H8" s="1" t="s">
+        <v>524</v>
+      </c>
+      <c r="I8" s="1" t="s">
+        <v>535</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>460</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>471</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>482</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>493</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="G9" s="1" t="s">
+        <v>514</v>
+      </c>
+      <c r="H9" s="1" t="s">
+        <v>525</v>
+      </c>
+      <c r="I9" s="1" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>461</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>472</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>483</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="G10" s="1" t="s">
+        <v>515</v>
+      </c>
+      <c r="H10" s="1" t="s">
+        <v>526</v>
+      </c>
+      <c r="I10" s="1" t="s">
+        <v>537</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>462</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>473</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>484</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>495</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="G11" s="1" t="s">
+        <v>516</v>
+      </c>
+      <c r="H11" s="1" t="s">
+        <v>527</v>
+      </c>
+      <c r="I11" s="1" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>463</v>
+      </c>
+      <c r="C12" s="1" t="s">
+        <v>474</v>
+      </c>
+      <c r="D12" s="1" t="s">
+        <v>485</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>494</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="G12" s="1" t="s">
+        <v>517</v>
+      </c>
+      <c r="H12" s="1" t="s">
+        <v>528</v>
+      </c>
+      <c r="I12" s="1" t="s">
+        <v>539</v>
       </c>
     </row>
   </sheetData>
